--- a/site/Integration-Studio-Guide/headings.xlsx
+++ b/site/Integration-Studio-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,73 +793,73 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Expression Builder - End-User Behaviour</t>
+          <t>Find and Replace Options in Code Editors</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K5EANN1V7MVNHHSEX89TXR0M</t>
+          <t>h_01KHN5P0877AK8DG2RBQY9233P</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5EANN1V7MVNHHSEX89TXR0M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN5P0877AK8DG2RBQY9233P</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analyze and Preview</t>
+          <t>Rule Builder - End User Behaviour</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
+          <t>h_01KHNGPZP1EMB25CVZTWNR9J49</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNGPZP1EMB25CVZTWNR9J49</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Adding Parameters to the Group of Parameters</t>
+          <t>Adding a Rule</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KD2B09DA6A6Q2QW9RK242X4G</t>
+          <t>h_01KHQY4N62Y4JCA2KTWGSMP7HQ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2B09DA6A6Q2QW9RK242X4G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQY4N62Y4JCA2KTWGSMP7HQ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sample Script with Group of Parameters</t>
+          <t>Assign On Column</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,151 +869,151 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KE6B6G11B36WSX78EHX4877A</t>
+          <t>h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KE6B6G11B36WSX78EHX4877A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Group of Parameters - End-User Behaviour</t>
+          <t>Defining Source Attribute Condition</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
+          <t>h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Email Template with AI - End-User Behaviour</t>
+          <t>Target Attribute Assignment</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
+          <t>h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Adding Rows</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
+          <t>h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Add a Group</t>
+          <t>Row Options</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Delete a Group</t>
+          <t>Expression Builder - End User Behaviour</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>h_01K5EANN1V7MVNHHSEX89TXR0M</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5EANN1V7MVNHHSEX89TXR0M</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Subgroups</t>
+          <t>Providing the User Prompt</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Add a Subgroup</t>
+          <t>Adding Parameters to the Group of Parameters</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>h_01KD2B09DA6A6Q2QW9RK242X4G</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2B09DA6A6Q2QW9RK242X4G</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Delete a Subgroup</t>
+          <t>Sample Script with Group of Parameters</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>h_01KE6B6G11B36WSX78EHX4877A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KE6B6G11B36WSX78EHX4877A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Group of Parameters - End User Behaviour</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Add a Section</t>
+          <t>Email Template with AI - End User Behaviour</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,107 +1089,107 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Delete a Section</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Configuration Panel in Expanded Mode</t>
+          <t>Add a Group</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Add Parameters</t>
+          <t>Delete a Group</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rearranging the Parameters</t>
+          <t>Subgroups</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Add Groups</t>
+          <t>Add a Subgroup</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,41 +1199,41 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Add Subgroups</t>
+          <t>Delete a Subgroup</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Add Sections</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,63 +1243,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Add a Section</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Create an Attribute Map</t>
+          <t>Delete a Section</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Configuration Panel in Expanded Mode</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,19 +1309,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Event Trigger</t>
+          <t>Add Parameters</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1331,63 +1331,63 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Schedule Trigger</t>
+          <t>Rearranging the Parameters</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Add Groups</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Add Tables in Integration</t>
+          <t>Add Subgroups</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1397,19 +1397,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Setting Table Accessibility for End Users</t>
+          <t>Add Sections</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,19 +1419,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Integration Details</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1441,41 +1441,41 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Navigating to the Sections on the Configuration Panel</t>
+          <t>Create an Attribute Map</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Target Attributes</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1485,63 +1485,63 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Source Attributes</t>
+          <t>Event Trigger</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mapping Options</t>
+          <t>Schedule Trigger</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Search by Attribute Names</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1551,85 +1551,85 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Modify Attribute Mapping via JSON</t>
+          <t>Add Tables in Integration</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Refresh Attribute Mapping</t>
+          <t>Hide Tables for Customers</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Using Tables in Attribute Map</t>
+          <t>Setting Table Accessibility for End Users</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Using Parameters in Attribute Map</t>
+          <t>Integration Details</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1639,19 +1639,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Preview in Attribute Map</t>
+          <t>Navigating to the Sections on the Configuration Panel</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1661,41 +1661,41 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Script Panel</t>
+          <t>Target Attributes</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Using AI Assistant for a Piece of Code</t>
+          <t>Source Attributes</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1705,19 +1705,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Show Difference in Script</t>
+          <t>Mapping Options</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1727,85 +1727,85 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Flow Chart Panel</t>
+          <t>Search by Attribute Names</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Documentation Panel</t>
+          <t>Modify Attribute Mapping via JSON</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Assistant Panel</t>
+          <t>Refresh Attribute Mapping</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Chat History</t>
+          <t>Using Tables in Attribute Map</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1815,19 +1815,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Use Generated Code in Script</t>
+          <t>Using Parameters in Attribute Map</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Use Parameters as Input</t>
+          <t>Data Preview in Attribute Map</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1859,41 +1859,41 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Use Event Types as Input</t>
+          <t>Script Panel</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Use Tables as Input</t>
+          <t>Using AI Assistant for a Piece of Code</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1903,19 +1903,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Upload File as Input</t>
+          <t>Show Difference in Script</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1925,41 +1925,41 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Feedback to the Assistant Response</t>
+          <t>Flow Chart Panel</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Summary Panel</t>
+          <t>Documentation Panel</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1969,32 +1969,230 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>Assistant Panel</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Chat History</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Use Generated Code in Script</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Use Parameters as Input</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Use Event Types as Input</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Use Tables as Input</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Upload File as Input</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Feedback to the Assistant Response</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Summary Panel</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>User Actions on Integrations</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>

--- a/site/Integration-Studio-Guide/headings.xlsx
+++ b/site/Integration-Studio-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -969,7 +969,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Expression Builder - End User Behaviour</t>
+          <t>OU Assignments Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,41 +979,41 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K5EANN1V7MVNHHSEX89TXR0M</t>
+          <t>h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5EANN1V7MVNHHSEX89TXR0M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Providing the User Prompt</t>
+          <t>Group Assignments Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
+          <t>h_01KKXWT5YB697969FP8ZF9K74B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXWT5YB697969FP8ZF9K74B</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Adding Parameters to the Group of Parameters</t>
+          <t>Expression Builder - End User Behaviour</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KD2B09DA6A6Q2QW9RK242X4G</t>
+          <t>h_01K5EANN1V7MVNHHSEX89TXR0M</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2B09DA6A6Q2QW9RK242X4G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5EANN1V7MVNHHSEX89TXR0M</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sample Script with Group of Parameters</t>
+          <t>Providing the User Prompt</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KE6B6G11B36WSX78EHX4877A</t>
+          <t>h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KE6B6G11B36WSX78EHX4877A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Group of Parameters - End User Behaviour</t>
+          <t>Adding Parameters to the Group of Parameters</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
+          <t>h_01KD2B09DA6A6Q2QW9RK242X4G</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2B09DA6A6Q2QW9RK242X4G</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Email Template with AI - End User Behaviour</t>
+          <t>Sample Script with Group of Parameters</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
+          <t>h_01KE6B6G11B36WSX78EHX4877A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KE6B6G11B36WSX78EHX4877A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Group of Parameters - End User Behaviour</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
+          <t>h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Add a Group</t>
+          <t>Email Template with AI - End User Behaviour</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,107 +1133,107 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Delete a Group</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Subgroups</t>
+          <t>Add a Group</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Add a Subgroup</t>
+          <t>Delete a Group</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Delete a Subgroup</t>
+          <t>Subgroups</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Add a Subgroup</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,129 +1243,129 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Add a Section</t>
+          <t>Delete a Subgroup</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Delete a Section</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Configuration Panel in Expanded Mode</t>
+          <t>Add a Section</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Add Parameters</t>
+          <t>Delete a Section</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Rearranging the Parameters</t>
+          <t>Configuration Panel in Expanded Mode</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Add Groups</t>
+          <t>Add Parameters</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1375,41 +1375,41 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Add Subgroups</t>
+          <t>Rearranging the Parameters</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Add Sections</t>
+          <t>Add Groups</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,41 +1419,41 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Add Subgroups</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Create an Attribute Map</t>
+          <t>Add Sections</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,19 +1463,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Event Trigger</t>
+          <t>Create an Attribute Map</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1507,19 +1507,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Schedule Trigger</t>
+          <t>Attribute Map Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1529,19 +1529,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1551,19 +1551,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Add Tables in Integration</t>
+          <t>Event Trigger</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1573,19 +1573,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Hide Tables for Customers</t>
+          <t>Schedule Trigger</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1595,107 +1595,107 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Setting Table Accessibility for End Users</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Integration Details</t>
+          <t>Add Tables in Integration</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Navigating to the Sections on the Configuration Panel</t>
+          <t>Hide Tables for Customers</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Target Attributes</t>
+          <t>Setting Table Accessibility for End Users</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Source Attributes</t>
+          <t>Integration Details</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1705,19 +1705,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mapping Options</t>
+          <t>Navigating to the Sections on the Configuration Panel</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1727,19 +1727,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Search by Attribute Names</t>
+          <t>Target Attributes</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1749,19 +1749,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Modify Attribute Mapping via JSON</t>
+          <t>Source Attributes</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1771,19 +1771,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Refresh Attribute Mapping</t>
+          <t>Mapping Options</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1793,19 +1793,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Using Tables in Attribute Map</t>
+          <t>Search by Attribute Names</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1815,19 +1815,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Using Parameters in Attribute Map</t>
+          <t>Modify Attribute Mapping via JSON</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Preview in Attribute Map</t>
+          <t>Refresh Attribute Mapping</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1859,41 +1859,41 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Script Panel</t>
+          <t>Using Tables in Attribute Map</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Using AI Assistant for a Piece of Code</t>
+          <t>Using Parameters in Attribute Map</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1903,19 +1903,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Show Difference in Script</t>
+          <t>Data Preview in Attribute Map</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1925,19 +1925,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Flow Chart Panel</t>
+          <t>Script Panel</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1947,129 +1947,129 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Documentation Panel</t>
+          <t>Using AI Assistant for a Piece of Code</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Assistant Panel</t>
+          <t>Show Difference in Script</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Chat History</t>
+          <t>Flow Chart Panel</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Use Generated Code in Script</t>
+          <t>Documentation Panel</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Use Parameters as Input</t>
+          <t>Assistant Panel</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Use Event Types as Input</t>
+          <t>Chat History</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2079,19 +2079,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Use Tables as Input</t>
+          <t>Use Generated Code in Script</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2101,19 +2101,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Upload File as Input</t>
+          <t>Use Parameters as Input</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2123,19 +2123,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Feedback to the Assistant Response</t>
+          <t>Use Event Types as Input</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2145,54 +2145,120 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Summary Panel</t>
+          <t>Use Tables as Input</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>Upload File as Input</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Feedback to the Assistant Response</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Summary Panel</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>User Actions on Integrations</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>

--- a/site/Integration-Studio-Guide/headings.xlsx
+++ b/site/Integration-Studio-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1607,51 +1607,51 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Disable or Enable Scheduled Runs</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>h_01KN3VJYX1RST87W49YTJNXT7Q</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KN3VJYX1RST87W49YTJNXT7Q</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Add Tables in Integration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hide Tables for Customers</t>
+          <t>Add Tables in Integration</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1661,19 +1661,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Setting Table Accessibility for End Users</t>
+          <t>Hide Tables for Customers</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1683,41 +1683,41 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Integration Details</t>
+          <t>Setting Table Accessibility for End Users</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Navigating to the Sections on the Configuration Panel</t>
+          <t>Integration Details</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1727,19 +1727,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Target Attributes</t>
+          <t>Navigating to the Sections on the Configuration Panel</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1749,19 +1749,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Source Attributes</t>
+          <t>Target Attributes</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1771,19 +1771,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mapping Options</t>
+          <t>Source Attributes</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1793,19 +1793,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Search by Attribute Names</t>
+          <t>Mapping Options</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1815,19 +1815,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Modify Attribute Mapping via JSON</t>
+          <t>Search by Attribute Names</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Refresh Attribute Mapping</t>
+          <t>Modify Attribute Mapping via JSON</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1859,19 +1859,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Using Tables in Attribute Map</t>
+          <t>Refresh Attribute Mapping</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Using Parameters in Attribute Map</t>
+          <t>Using Tables in Attribute Map</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1903,19 +1903,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Preview in Attribute Map</t>
+          <t>Using Parameters in Attribute Map</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1925,63 +1925,63 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Script Panel</t>
+          <t>Data Preview in Attribute Map</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Using AI Assistant for a Piece of Code</t>
+          <t>Script Panel</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Show Difference in Script</t>
+          <t>Using AI Assistant for a Piece of Code</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1991,41 +1991,41 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Flow Chart Panel</t>
+          <t>Show Difference in Script</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Documentation Panel</t>
+          <t>Flow Chart Panel</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2035,19 +2035,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Assistant Panel</t>
+          <t>Documentation Panel</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2057,41 +2057,41 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Chat History</t>
+          <t>Assistant Panel</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Use Generated Code in Script</t>
+          <t>Chat History</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2101,19 +2101,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Use Parameters as Input</t>
+          <t>Use Generated Code in Script</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2123,19 +2123,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Use Event Types as Input</t>
+          <t>Use Parameters as Input</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2145,19 +2145,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Use Tables as Input</t>
+          <t>Use Event Types as Input</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2167,19 +2167,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Upload File as Input</t>
+          <t>Use Tables as Input</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2189,19 +2189,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Feedback to the Assistant Response</t>
+          <t>Upload File as Input</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2211,54 +2211,76 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Summary Panel</t>
+          <t>Feedback to the Assistant Response</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>Summary Panel</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>User Actions on Integrations</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>

--- a/site/Integration-Studio-Guide/headings.xlsx
+++ b/site/Integration-Studio-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -859,7 +859,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Assign On Column</t>
+          <t>Deleting a Rule</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
+          <t>h_01KP7Y9E8ASFQY568SS1JNSD04</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KP7Y9E8ASFQY568SS1JNSD04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Defining Source Attribute Condition</t>
+          <t>Assign On Column</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
+          <t>h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Target Attribute Assignment</t>
+          <t>Defining Source Attribute Condition</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
+          <t>h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Adding Rows</t>
+          <t>Target Attribute Assignment</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
+          <t>h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Row Options</t>
+          <t>Adding Rows</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,41 +957,41 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
+          <t>h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OU Assignments Analysis - End User Behaviour</t>
+          <t>Row Options</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
+          <t>h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Group Assignments Analysis - End User Behaviour</t>
+          <t>OU Assignments Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,19 +1001,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KKXWT5YB697969FP8ZF9K74B</t>
+          <t>h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXWT5YB697969FP8ZF9K74B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Expression Builder - End User Behaviour</t>
+          <t>Group Assignments Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,63 +1023,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K5EANN1V7MVNHHSEX89TXR0M</t>
+          <t>h_01KKXWT5YB697969FP8ZF9K74B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5EANN1V7MVNHHSEX89TXR0M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXWT5YB697969FP8ZF9K74B</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Providing the User Prompt</t>
+          <t>Expression Builder - End User Behaviour</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
+          <t>h_01K5EANN1V7MVNHHSEX89TXR0M</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5EANN1V7MVNHHSEX89TXR0M</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Adding Parameters to the Group of Parameters</t>
+          <t>Table Support in Expression Builder</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KD2B09DA6A6Q2QW9RK242X4G</t>
+          <t>h_01KP86XMYB27P4B4CG2AZWF1V0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2B09DA6A6Q2QW9RK242X4G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KP86XMYB27P4B4CG2AZWF1V0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sample Script with Group of Parameters</t>
+          <t>Providing the User Prompt</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,19 +1089,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KE6B6G11B36WSX78EHX4877A</t>
+          <t>h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KE6B6G11B36WSX78EHX4877A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Group of Parameters - End User Behaviour</t>
+          <t>Adding Parameters to the Group of Parameters</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,63 +1111,63 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
+          <t>h_01KD2B09DA6A6Q2QW9RK242X4G</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2B09DA6A6Q2QW9RK242X4G</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Email Template with AI - End User Behaviour</t>
+          <t>Sample Script with Group of Parameters</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
+          <t>h_01KE6B6G11B36WSX78EHX4877A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KE6B6G11B36WSX78EHX4877A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Group of Parameters - End User Behaviour</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
+          <t>h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Add a Group</t>
+          <t>Email Template with AI - End User Behaviour</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,107 +1177,107 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Delete a Group</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Subgroups</t>
+          <t>Add a Group</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Add a Subgroup</t>
+          <t>Delete a Group</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Delete a Subgroup</t>
+          <t>Subgroups</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Add a Subgroup</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1287,129 +1287,129 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Add a Section</t>
+          <t>Delete a Subgroup</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Delete a Section</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Configuration Panel in Expanded Mode</t>
+          <t>Add a Section</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Add Parameters</t>
+          <t>Delete a Section</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Rearranging the Parameters</t>
+          <t>Configuration Panel in Expanded Mode</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Add Groups</t>
+          <t>Add Parameters</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,41 +1419,41 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Add Subgroups</t>
+          <t>Rearranging the Parameters</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Add Sections</t>
+          <t>Add Groups</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,41 +1463,41 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Add Subgroups</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Create an Attribute Map</t>
+          <t>Add Sections</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1507,63 +1507,63 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Attribute Map Analysis - End User Behaviour</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
+          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Create an Attribute Map</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Event Trigger</t>
+          <t>Attribute Map Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1573,129 +1573,129 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Schedule Trigger</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Disable or Enable Scheduled Runs</t>
+          <t>Event Trigger</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01KN3VJYX1RST87W49YTJNXT7Q</t>
+          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KN3VJYX1RST87W49YTJNXT7Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule Trigger</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Add Tables in Integration</t>
+          <t>Disable or Enable Scheduled Runs</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>h_01KN3VJYX1RST87W49YTJNXT7Q</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KN3VJYX1RST87W49YTJNXT7Q</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Hide Tables for Customers</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Setting Table Accessibility for End Users</t>
+          <t>Add Tables in Integration</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1705,63 +1705,63 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Integration Details</t>
+          <t>Hide Tables for Customers</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Navigating to the Sections on the Configuration Panel</t>
+          <t>Setting Table Accessibility for End Users</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Target Attributes</t>
+          <t>Integration Details</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1771,19 +1771,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Source Attributes</t>
+          <t>Navigating to the Sections on the Configuration Panel</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1793,19 +1793,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mapping Options</t>
+          <t>Target Attributes</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1815,19 +1815,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Search by Attribute Names</t>
+          <t>Source Attributes</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Modify Attribute Mapping via JSON</t>
+          <t>Mapping Options</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1859,19 +1859,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Refresh Attribute Mapping</t>
+          <t>Search by Attribute Names</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Using Tables in Attribute Map</t>
+          <t>Modify Attribute Mapping via JSON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1903,19 +1903,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Using Parameters in Attribute Map</t>
+          <t>Refresh Attribute Mapping</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1925,19 +1925,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Preview in Attribute Map</t>
+          <t>Using Tables in Attribute Map</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1947,41 +1947,41 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Script Panel</t>
+          <t>Using Parameters in Attribute Map</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Using AI Assistant for a Piece of Code</t>
+          <t>Data Preview in Attribute Map</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1991,85 +1991,85 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Show Difference in Script</t>
+          <t>Script Panel</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Flow Chart Panel</t>
+          <t>Using AI Assistant for a Piece of Code</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Documentation Panel</t>
+          <t>Show Difference in Script</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Assistant Panel</t>
+          <t>Flow Chart Panel</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2079,63 +2079,63 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Chat History</t>
+          <t>Documentation Panel</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Use Generated Code in Script</t>
+          <t>Assistant Panel</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Use Parameters as Input</t>
+          <t>Chat History</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2145,19 +2145,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Use Event Types as Input</t>
+          <t>Use Generated Code in Script</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2167,19 +2167,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Use Tables as Input</t>
+          <t>Use Parameters as Input</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2189,19 +2189,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Upload File as Input</t>
+          <t>Use Event Types as Input</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Feedback to the Assistant Response</t>
+          <t>Use Tables as Input</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2233,54 +2233,98 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Summary Panel</t>
+          <t>Upload File as Input</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Feedback to the Assistant Response</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Summary Panel</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>User Actions on Integrations</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>

--- a/site/Integration-Studio-Guide/headings.xlsx
+++ b/site/Integration-Studio-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2003,7 +2003,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Script Panel</t>
+          <t>Script Editor Panel</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2025,29 +2025,29 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Using AI Assistant for a Piece of Code</t>
+          <t>Code Suggestions</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Show Difference in Script</t>
+          <t>Using AI Assistant for a Piece of Code</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2057,41 +2057,41 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Flow Chart Panel</t>
+          <t>Show Difference in Script</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Documentation Panel</t>
+          <t>Flow Chart Panel</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2101,19 +2101,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Assistant Panel</t>
+          <t>Documentation Panel</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2123,41 +2123,41 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Chat History</t>
+          <t>Assistant Panel</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Use Generated Code in Script</t>
+          <t>Chat History</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2167,19 +2167,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Use Parameters as Input</t>
+          <t>Use Generated Code in Script</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2189,19 +2189,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Use Event Types as Input</t>
+          <t>Use Parameters as Input</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Use Tables as Input</t>
+          <t>Use Event Types as Input</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2233,19 +2233,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Upload File as Input</t>
+          <t>Use Tables as Input</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2255,19 +2255,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Feedback to the Assistant Response</t>
+          <t>Upload File as Input</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2277,54 +2277,76 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Summary Panel</t>
+          <t>Feedback to the Assistant Response</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>Summary Panel</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>User Actions on Integrations</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>

--- a/site/Integration-Studio-Guide/headings.xlsx
+++ b/site/Integration-Studio-Guide/headings.xlsx
@@ -1101,7 +1101,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Adding Parameters to the Group of Parameters</t>
+          <t>Adding Parameters (Attributes) to the Group of Parameters</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">

--- a/site/Integration-Studio-Guide/headings.xlsx
+++ b/site/Integration-Studio-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,95 +529,95 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Configuration Panel</t>
+          <t>Unsaved Changes Confirmation</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01HVGBWBA9G469AFTPS8QX2X7M</t>
+          <t>h_01KQY1VKAKDV9TJB812TFYQ1JS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01HVGBWBA9G469AFTPS8QX2X7M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY1VKAKDV9TJB812TFYQ1JS</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>Configuration Panel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01J7X6HF7RM0AC55GDVR6P4V60</t>
+          <t>h_01HVGBWBA9G469AFTPS8QX2X7M</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7X6HF7RM0AC55GDVR6P4V60</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01HVGBWBA9G469AFTPS8QX2X7M</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Refresh Application</t>
+          <t>Applications</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01JH86395BJZ49DXNGHB8Z0TNQ</t>
+          <t>h_01J7X6HF7RM0AC55GDVR6P4V60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JH86395BJZ49DXNGHB8Z0TNQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7X6HF7RM0AC55GDVR6P4V60</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Persistent Variables</t>
+          <t>Add Application</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01K0646AEDPDSFF6WD66CA97Y1</t>
+          <t>h_01KQVTDNSR3EC7XP0R6DQGXGN3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0646AEDPDSFF6WD66CA97Y1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQVTDNSR3EC7XP0R6DQGXGN3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Add a Persistent Variable</t>
+          <t>Refresh Application</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,41 +627,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01K064M0SMQ27TPRCKAMWWSAV6</t>
+          <t>h_01JH86395BJZ49DXNGHB8Z0TNQ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K064M0SMQ27TPRCKAMWWSAV6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JH86395BJZ49DXNGHB8Z0TNQ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Unlinking a Persistent Variable from an Integration</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01K06FHCFKP8066EFD02VVPCP0</t>
+          <t>h_01JC37BP3X13J4TXDJFDJ8MV2D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K06FHCFKP8066EFD02VVPCP0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JC37BP3X13J4TXDJFDJ8MV2D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Viewing the Global List of Persistent Variables</t>
+          <t>Add a Parameter</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01K06FB859P9PN48PNX6MHAXGF</t>
+          <t>h_01JT87ME8H4DCFWBEVT41R0P3V</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K06FB859P9PN48PNX6MHAXGF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87ME8H4DCFWBEVT41R0P3V</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deleting a Persistent Variable</t>
+          <t>Rearranging the Parameters</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,63 +693,63 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K06M05S3XBJ3F39WN29RJ0J8</t>
+          <t>h_01K0755R59TR9717AM1EHGDR58</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K06M05S3XBJ3F39WN29RJ0J8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0755R59TR9717AM1EHGDR58</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Add a Divider</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01JC37BP3X13J4TXDJFDJ8MV2D</t>
+          <t>h_01KQY242R3X8CKSKF3EMGA3KB8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JC37BP3X13J4TXDJFDJ8MV2D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY242R3X8CKSKF3EMGA3KB8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Add a Parameter</t>
+          <t>Searching for a Parameter</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01JT87ME8H4DCFWBEVT41R0P3V</t>
+          <t>h_01K9423F049CHHT4Y69D56M4ZH</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87ME8H4DCFWBEVT41R0P3V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K9423F049CHHT4Y69D56M4ZH</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rearranging the Parameters</t>
+          <t>Find and Replace Options in Code Editors</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,41 +759,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01K0755R59TR9717AM1EHGDR58</t>
+          <t>h_01KHN5P0877AK8DG2RBQY9233P</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0755R59TR9717AM1EHGDR58</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN5P0877AK8DG2RBQY9233P</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Searching for a Parameter</t>
+          <t>Rule Builder - End User Behaviour</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K9423F049CHHT4Y69D56M4ZH</t>
+          <t>h_01KHNGPZP1EMB25CVZTWNR9J49</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K9423F049CHHT4Y69D56M4ZH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNGPZP1EMB25CVZTWNR9J49</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Find and Replace Options in Code Editors</t>
+          <t>Enable or Disable Rules</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,41 +803,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHN5P0877AK8DG2RBQY9233P</t>
+          <t>h_01KQVNXFP66RD3S780Y08E2SPN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN5P0877AK8DG2RBQY9233P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQVNXFP66RD3S780Y08E2SPN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rule Builder - End User Behaviour</t>
+          <t>Adding a Rule</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHNGPZP1EMB25CVZTWNR9J49</t>
+          <t>h_01KHQY4N62Y4JCA2KTWGSMP7HQ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNGPZP1EMB25CVZTWNR9J49</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQY4N62Y4JCA2KTWGSMP7HQ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Adding a Rule</t>
+          <t>Rules Pagination</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,12 +847,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KHQY4N62Y4JCA2KTWGSMP7HQ</t>
+          <t>h_01KQVRZ2WCV5G7TNE2ZDBSAZZT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQY4N62Y4JCA2KTWGSMP7HQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQVRZ2WCV5G7TNE2ZDBSAZZT</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Link Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1211,139 +1211,139 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Add a Group</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>h_01KQY63RM5RV0QHYSGKWJBE85W</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY63RM5RV0QHYSGKWJBE85W</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Delete a Group</t>
+          <t>Add a Group</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Subgroups</t>
+          <t>Delete a Group</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Add a Subgroup</t>
+          <t>Subgroups</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Delete a Subgroup</t>
+          <t>Add a Subgroup</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Delete a Subgroup</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Add a Section</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,107 +1353,107 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Delete a Section</t>
+          <t>Add a Section</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Configuration Panel in Expanded Mode</t>
+          <t>Delete a Section</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Add Parameters</t>
+          <t>Collapsed by Default for Sections</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>h_01KQY345D9TRQSQ65BXDNGCT56</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY345D9TRQSQ65BXDNGCT56</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Rearranging the Parameters</t>
+          <t>Configuration Panel in Expanded Mode</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Add Groups</t>
+          <t>Add Parameters</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,41 +1463,41 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Add Subgroups</t>
+          <t>Rearranging the Parameters</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Add Sections</t>
+          <t>Add Groups</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1507,41 +1507,41 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Add Subgroups</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Create an Attribute Map</t>
+          <t>Add Sections</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1551,63 +1551,63 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Attribute Map Analysis - End User Behaviour</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
+          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Create an Attribute Map</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Event Trigger</t>
+          <t>Attribute Map Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1617,129 +1617,129 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Schedule Trigger</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Disable or Enable Scheduled Runs</t>
+          <t>Event Trigger</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01KN3VJYX1RST87W49YTJNXT7Q</t>
+          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KN3VJYX1RST87W49YTJNXT7Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule Trigger</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Add Tables in Integration</t>
+          <t>Disable or Enable Scheduled Runs</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>h_01KN3VJYX1RST87W49YTJNXT7Q</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KN3VJYX1RST87W49YTJNXT7Q</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Hide Tables for Customers</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Setting Table Accessibility for End Users</t>
+          <t>Add Tables in Integration</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1749,63 +1749,63 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Integration Details</t>
+          <t>Hide Tables for Customers</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Navigating to the Sections on the Configuration Panel</t>
+          <t>Setting Table Accessibility for End Users</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Target Attributes</t>
+          <t>Integration Details</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1815,19 +1815,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Source Attributes</t>
+          <t>Navigating to the Sections on the Configuration Panel</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mapping Options</t>
+          <t>Target Attributes</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1859,19 +1859,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Search by Attribute Names</t>
+          <t>Source Attributes</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Modify Attribute Mapping via JSON</t>
+          <t>Mapping Options</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1903,19 +1903,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Refresh Attribute Mapping</t>
+          <t>Search by Attribute Names</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1925,19 +1925,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Using Tables in Attribute Map</t>
+          <t>Modify Attribute Mapping via JSON</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1947,19 +1947,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Using Parameters in Attribute Map</t>
+          <t>Refresh Attribute Mapping</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1969,19 +1969,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Preview in Attribute Map</t>
+          <t>Using Tables in Attribute Map</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1991,151 +1991,151 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Script Editor Panel</t>
+          <t>Using Parameters in Attribute Map</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Code Suggestions</t>
+          <t>Data Preview in Attribute Map</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
+          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Using AI Assistant for a Piece of Code</t>
+          <t>Script Editor Panel</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Show Difference in Script</t>
+          <t>Code Suggestions</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Flow Chart Panel</t>
+          <t>Using AI Assistant for a Piece of Code</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Documentation Panel</t>
+          <t>Show Difference in Script</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Assistant Panel</t>
+          <t>Flow Chart Panel</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2145,63 +2145,63 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Chat History</t>
+          <t>Documentation Panel</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Use Generated Code in Script</t>
+          <t>Assistant Panel</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Use Parameters as Input</t>
+          <t>Chat History</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Use Event Types as Input</t>
+          <t>Use Generated Code in Script</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2233,19 +2233,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Use Tables as Input</t>
+          <t>Use Parameters as Input</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2255,19 +2255,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Upload File as Input</t>
+          <t>Use Event Types as Input</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2277,19 +2277,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Feedback to the Assistant Response</t>
+          <t>Use Tables as Input</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2299,54 +2299,98 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Summary Panel</t>
+          <t>Upload File as Input</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>Feedback to the Assistant Response</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Summary Panel</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>User Actions on Integrations</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>

--- a/site/Integration-Studio-Guide/headings.xlsx
+++ b/site/Integration-Studio-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,29 +683,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rearranging the Parameters</t>
+          <t>Sample Script</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01K0755R59TR9717AM1EHGDR58</t>
+          <t>h_01KSPAZ5C1G8E5CGX4XKHE7MZ3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0755R59TR9717AM1EHGDR58</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KSPAZ5C1G8E5CGX4XKHE7MZ3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Add a Divider</t>
+          <t>Rearranging the Parameters</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KQY242R3X8CKSKF3EMGA3KB8</t>
+          <t>h_01K0755R59TR9717AM1EHGDR58</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY242R3X8CKSKF3EMGA3KB8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0755R59TR9717AM1EHGDR58</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Searching for a Parameter</t>
+          <t>Add a Divider</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01K9423F049CHHT4Y69D56M4ZH</t>
+          <t>h_01KQY242R3X8CKSKF3EMGA3KB8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K9423F049CHHT4Y69D56M4ZH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY242R3X8CKSKF3EMGA3KB8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Find and Replace Options in Code Editors</t>
+          <t>Searching for a Parameter</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,63 +759,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KHN5P0877AK8DG2RBQY9233P</t>
+          <t>h_01K9423F049CHHT4Y69D56M4ZH</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN5P0877AK8DG2RBQY9233P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K9423F049CHHT4Y69D56M4ZH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rule Builder - End User Behaviour</t>
+          <t>Find and Replace Options in Code Editors</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHNGPZP1EMB25CVZTWNR9J49</t>
+          <t>h_01KHN5P0877AK8DG2RBQY9233P</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNGPZP1EMB25CVZTWNR9J49</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN5P0877AK8DG2RBQY9233P</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enable or Disable Rules</t>
+          <t>Rule Builder - End User Behaviour</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KQVNXFP66RD3S780Y08E2SPN</t>
+          <t>h_01KHNGPZP1EMB25CVZTWNR9J49</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQVNXFP66RD3S780Y08E2SPN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNGPZP1EMB25CVZTWNR9J49</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Adding a Rule</t>
+          <t>Enable or Disable Rules</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHQY4N62Y4JCA2KTWGSMP7HQ</t>
+          <t>h_01KQVNXFP66RD3S780Y08E2SPN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQY4N62Y4JCA2KTWGSMP7HQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQVNXFP66RD3S780Y08E2SPN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rules Pagination</t>
+          <t>Adding a Rule</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KQVRZ2WCV5G7TNE2ZDBSAZZT</t>
+          <t>h_01KHQY4N62Y4JCA2KTWGSMP7HQ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQVRZ2WCV5G7TNE2ZDBSAZZT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQY4N62Y4JCA2KTWGSMP7HQ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deleting a Rule</t>
+          <t>Rules Pagination</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KP7Y9E8ASFQY568SS1JNSD04</t>
+          <t>h_01KQVRZ2WCV5G7TNE2ZDBSAZZT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KP7Y9E8ASFQY568SS1JNSD04</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQVRZ2WCV5G7TNE2ZDBSAZZT</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Assign On Column</t>
+          <t>Deleting a Rule</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
+          <t>h_01KP7Y9E8ASFQY568SS1JNSD04</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KP7Y9E8ASFQY568SS1JNSD04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Defining Source Attribute Condition</t>
+          <t>Assign On Column</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
+          <t>h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Target Attribute Assignment</t>
+          <t>Defining Source Attribute Condition</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
+          <t>h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Adding Rows</t>
+          <t>Target Attribute Assignment</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
+          <t>h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Row Options</t>
+          <t>Adding Rows</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,41 +979,41 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
+          <t>h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OU Assignments Analysis - End User Behaviour</t>
+          <t>Row Options</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
+          <t>h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Group Assignments Analysis - End User Behaviour</t>
+          <t>OU Assignments Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KKXWT5YB697969FP8ZF9K74B</t>
+          <t>h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXWT5YB697969FP8ZF9K74B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Expression Builder - End User Behaviour</t>
+          <t>Group Assignments Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,41 +1045,41 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01K5EANN1V7MVNHHSEX89TXR0M</t>
+          <t>h_01KKXWT5YB697969FP8ZF9K74B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5EANN1V7MVNHHSEX89TXR0M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXWT5YB697969FP8ZF9K74B</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Table Support in Expression Builder</t>
+          <t>Expression Builder - End User Behaviour</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KP86XMYB27P4B4CG2AZWF1V0</t>
+          <t>h_01K5EANN1V7MVNHHSEX89TXR0M</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KP86XMYB27P4B4CG2AZWF1V0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5EANN1V7MVNHHSEX89TXR0M</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Providing the User Prompt</t>
+          <t>Table Support in Expression Builder</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,85 +1089,85 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
+          <t>h_01KP86XMYB27P4B4CG2AZWF1V0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KP86XMYB27P4B4CG2AZWF1V0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Adding Parameters (Attributes) to the Group of Parameters</t>
+          <t>Providing the User Prompt</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KD2B09DA6A6Q2QW9RK242X4G</t>
+          <t>h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2B09DA6A6Q2QW9RK242X4G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sample Script with Group of Parameters</t>
+          <t>Adding Parameters (Attributes) to the Group of Parameters</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KE6B6G11B36WSX78EHX4877A</t>
+          <t>h_01KD2B09DA6A6Q2QW9RK242X4G</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KE6B6G11B36WSX78EHX4877A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2B09DA6A6Q2QW9RK242X4G</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Group of Parameters - End User Behaviour</t>
+          <t>Sample Script with Group of Parameters</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
+          <t>h_01KE6B6G11B36WSX78EHX4877A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KE6B6G11B36WSX78EHX4877A</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Email Template with AI - End User Behaviour</t>
+          <t>Group of Parameters - End User Behaviour</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,41 +1177,41 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
+          <t>h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Link Analysis - End User Behaviour</t>
+          <t>Email Template with AI - End User Behaviour</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
+          <t>h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Link Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,151 +1221,151 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01KQY63RM5RV0QHYSGKWJBE85W</t>
+          <t>h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY63RM5RV0QHYSGKWJBE85W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Add a Group</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>h_01KQY63RM5RV0QHYSGKWJBE85W</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY63RM5RV0QHYSGKWJBE85W</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Delete a Group</t>
+          <t>Add a Group</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Subgroups</t>
+          <t>Delete a Group</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Add a Subgroup</t>
+          <t>Subgroups</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Delete a Subgroup</t>
+          <t>Add a Subgroup</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Delete a Subgroup</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Add a Section</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1375,41 +1375,41 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Delete a Section</t>
+          <t>Add a Section</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Collapsed by Default for Sections</t>
+          <t>Delete a Section</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,107 +1419,107 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KQY345D9TRQSQ65BXDNGCT56</t>
+          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY345D9TRQSQ65BXDNGCT56</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Configuration Panel in Expanded Mode</t>
+          <t>Collapsed by Default for Sections</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>h_01KQY345D9TRQSQ65BXDNGCT56</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY345D9TRQSQ65BXDNGCT56</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Add Parameters</t>
+          <t>Configuration Panel in Expanded Mode</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rearranging the Parameters</t>
+          <t>Add Parameters</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Add Groups</t>
+          <t>Rearranging the Parameters</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Add Subgroups</t>
+          <t>Add Groups</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1529,19 +1529,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Add Sections</t>
+          <t>Add Subgroups</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1551,63 +1551,63 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Add Sections</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Create an Attribute Map</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Attribute Map Analysis - End User Behaviour</t>
+          <t>Create an Attribute Map</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1617,41 +1617,41 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
+          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Script or JSON Mapping on Refresh</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>h_01KSNE06X1CQDVNKFBAGKV24AH</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KSNE06X1CQDVNKFBAGKV24AH</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Event Trigger</t>
+          <t>Attribute Map Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1661,129 +1661,129 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Schedule Trigger</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Disable or Enable Scheduled Runs</t>
+          <t>Event Trigger</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01KN3VJYX1RST87W49YTJNXT7Q</t>
+          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KN3VJYX1RST87W49YTJNXT7Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule Trigger</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Add Tables in Integration</t>
+          <t>Disable or Enable Scheduled Runs</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>h_01KN3VJYX1RST87W49YTJNXT7Q</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KN3VJYX1RST87W49YTJNXT7Q</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hide Tables for Customers</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Setting Table Accessibility for End Users</t>
+          <t>Add Tables in Integration</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1793,63 +1793,63 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Integration Details</t>
+          <t>Hide Tables for Customers</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Navigating to the Sections on the Configuration Panel</t>
+          <t>Setting Table Accessibility for End Users</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Target Attributes</t>
+          <t>Integration Details</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1859,19 +1859,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Source Attributes</t>
+          <t>Navigating to the Sections on the Configuration Panel</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mapping Options</t>
+          <t>Target Attributes</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1903,19 +1903,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Search by Attribute Names</t>
+          <t>Source Attributes</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1925,19 +1925,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Modify Attribute Mapping via JSON</t>
+          <t>Mapping Options</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1947,19 +1947,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Refresh Attribute Mapping</t>
+          <t>Search by Attribute Names</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1969,19 +1969,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Using Tables in Attribute Map</t>
+          <t>Modify Attribute Mapping via JSON</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1991,19 +1991,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Using Parameters in Attribute Map</t>
+          <t>Refresh Attribute Mapping</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2013,19 +2013,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Preview in Attribute Map</t>
+          <t>Using Tables in Attribute Map</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2035,151 +2035,151 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Script Editor Panel</t>
+          <t>Using Parameters in Attribute Map</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Code Suggestions</t>
+          <t>Data Preview in Attribute Map</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
+          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Using AI Assistant for a Piece of Code</t>
+          <t>Script Editor Panel</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Show Difference in Script</t>
+          <t>Code Suggestions</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Flow Chart Panel</t>
+          <t>Using AI Assistant for a Piece of Code</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Documentation Panel</t>
+          <t>Show Difference in Script</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Assistant Panel</t>
+          <t>Flow Chart Panel</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2189,63 +2189,63 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Chat History</t>
+          <t>Documentation Panel</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Use Generated Code in Script</t>
+          <t>Assistant Panel</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Use Parameters as Input</t>
+          <t>Chat History</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2255,19 +2255,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Use Event Types as Input</t>
+          <t>Use Generated Code in Script</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2277,19 +2277,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Use Tables as Input</t>
+          <t>Use Parameters as Input</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Upload File as Input</t>
+          <t>Use Event Types as Input</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2321,19 +2321,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Feedback to the Assistant Response</t>
+          <t>Use Tables as Input</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2343,54 +2343,98 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Summary Panel</t>
+          <t>Upload File as Input</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>Feedback to the Assistant Response</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Summary Panel</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>User Actions on Integrations</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
         </is>

--- a/site/Integration-Studio-Guide/headings.xlsx
+++ b/site/Integration-Studio-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,6 +2440,28 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Import Integration Access Control</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>h_01KT3D64S2S4H1K0SDRJMM5EQ6</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KT3D64S2S4H1K0SDRJMM5EQ6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Integration-Studio-Guide/headings.xlsx
+++ b/site/Integration-Studio-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -859,7 +859,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rules Pagination</t>
+          <t>Array Attribute Support in Rule Conditions</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KQVRZ2WCV5G7TNE2ZDBSAZZT</t>
+          <t>h_01KV7E78MQR150Q52RDV2BN5A8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQVRZ2WCV5G7TNE2ZDBSAZZT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KV7E78MQR150Q52RDV2BN5A8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deleting a Rule</t>
+          <t>Rules Pagination</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KP7Y9E8ASFQY568SS1JNSD04</t>
+          <t>h_01KQVRZ2WCV5G7TNE2ZDBSAZZT</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KP7Y9E8ASFQY568SS1JNSD04</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQVRZ2WCV5G7TNE2ZDBSAZZT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Assign On Column</t>
+          <t>Deleting a Rule</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
+          <t>h_01KP7Y9E8ASFQY568SS1JNSD04</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KP7Y9E8ASFQY568SS1JNSD04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Defining Source Attribute Condition</t>
+          <t>Assign On Column</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
+          <t>h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNH6MC2VNCBS8FVFN0HWMB</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Target Attribute Assignment</t>
+          <t>Defining Source Attribute Condition</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
+          <t>h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNHPT3ZTF1SH0S0HAAY45H</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Adding Rows</t>
+          <t>Target Attribute Assignment</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
+          <t>h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNNK18WQ3YDRVNFYF76FDR0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Row Options</t>
+          <t>Adding Rows</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
+          <t>h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHNPDYEXAMSGMHTVQ6N654K7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OU Assignments Analysis - End User Behaviour</t>
+          <t>Row Options</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
+          <t>h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHQXMFEJJD8MHAYE59DPWY8Z</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Group Assignments Analysis - End User Behaviour</t>
+          <t>OU Assignments Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KKXWT5YB697969FP8ZF9K74B</t>
+          <t>h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXWT5YB697969FP8ZF9K74B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXZYXX0F0FN0ZGNRP8MMB5K</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Expression Builder - End User Behaviour</t>
+          <t>Group Assignments Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,41 +1067,41 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K5EANN1V7MVNHHSEX89TXR0M</t>
+          <t>h_01KKXWT5YB697969FP8ZF9K74B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5EANN1V7MVNHHSEX89TXR0M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKXWT5YB697969FP8ZF9K74B</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Table Support in Expression Builder</t>
+          <t>Expression Builder - End User Behaviour</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KP86XMYB27P4B4CG2AZWF1V0</t>
+          <t>h_01K5EANN1V7MVNHHSEX89TXR0M</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KP86XMYB27P4B4CG2AZWF1V0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5EANN1V7MVNHHSEX89TXR0M</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Providing the User Prompt</t>
+          <t>Table Support in Expression Builder</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,85 +1111,85 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
+          <t>h_01KP86XMYB27P4B4CG2AZWF1V0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KP86XMYB27P4B4CG2AZWF1V0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Adding Parameters (Attributes) to the Group of Parameters</t>
+          <t>Providing the User Prompt</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01KD2B09DA6A6Q2QW9RK242X4G</t>
+          <t>h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2B09DA6A6Q2QW9RK242X4G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K5G57AG2G7ZYV6PPRWPWZW3N</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sample Script with Group of Parameters</t>
+          <t>Adding Parameters (Attributes) to the Group of Parameters</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01KE6B6G11B36WSX78EHX4877A</t>
+          <t>h_01KD2B09DA6A6Q2QW9RK242X4G</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KE6B6G11B36WSX78EHX4877A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2B09DA6A6Q2QW9RK242X4G</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Group of Parameters - End User Behaviour</t>
+          <t>Sample Script with Group of Parameters</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
+          <t>h_01KE6B6G11B36WSX78EHX4877A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KE6B6G11B36WSX78EHX4877A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Email Template with AI - End User Behaviour</t>
+          <t>Group of Parameters - End User Behaviour</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1199,41 +1199,41 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
+          <t>h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KD2CXNS5V4ACGGCJ7P3PPQTB</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Link Analysis - End User Behaviour</t>
+          <t>Email Template with AI - End User Behaviour</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
+          <t>h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KCTZ8YCFBKWK3YNYXHRCN1JC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Groups</t>
+          <t>Link Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,151 +1243,151 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01KQY63RM5RV0QHYSGKWJBE85W</t>
+          <t>h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY63RM5RV0QHYSGKWJBE85W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T2FWMB3AXSYJY52W7ZVJ8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Add a Group</t>
+          <t>Groups</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>h_01KQY63RM5RV0QHYSGKWJBE85W</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY63RM5RV0QHYSGKWJBE85W</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Delete a Group</t>
+          <t>Add a Group</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5D563FZPRDWH154M3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Subgroups</t>
+          <t>Delete a Group</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYJXMB6J0G49JHC1TYKM2MMX</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Add a Subgroup</t>
+          <t>Subgroups</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JYDSYWH5M4GFXMH0KVJTWJ8Y</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Delete a Subgroup</t>
+          <t>Add a Subgroup</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K03T3DPEN85H7JKTKCBER6ZF</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sections</t>
+          <t>Delete a Subgroup</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4JQ19QYVNQ97M7QSSG2P6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Add a Section</t>
+          <t>Sections</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1397,41 +1397,41 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K063N34NGS08AYGZSTASHN16</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Delete a Section</t>
+          <t>Add a Section</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JT87MAMDCCBDGVMT3T335F6A</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Collapsed by Default for Sections</t>
+          <t>Delete a Section</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1441,107 +1441,107 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01KQY345D9TRQSQ65BXDNGCT56</t>
+          <t>01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY345D9TRQSQ65BXDNGCT56</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01JYK4PFZPR4CZCAYCDE62HC29</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Configuration Panel in Expanded Mode</t>
+          <t>Collapsed by Default for Sections</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>h_01KQY345D9TRQSQ65BXDNGCT56</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KQY345D9TRQSQ65BXDNGCT56</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Add Parameters</t>
+          <t>Configuration Panel in Expanded Mode</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K070YNEM9AYZC9W628GF475W</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Rearranging the Parameters</t>
+          <t>Add Parameters</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K0740T2N9DNSTY2MX7T0GWV5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Add Groups</t>
+          <t>Rearranging the Parameters</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K30Z3KCE9RABKBBH45Z88A8P</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Add Subgroups</t>
+          <t>Add Groups</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1551,19 +1551,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08WX6E7FC39P8XCV32NM398</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Add Sections</t>
+          <t>Add Subgroups</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1573,63 +1573,63 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XDGBPM48YH52341WQ20T2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Add Sections</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K08XGESP6N5QRJKKZX4E8QKJ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Create an Attribute Map</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9X0PRJ41CB50QAJQATFKQF</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Script or JSON Mapping on Refresh</t>
+          <t>Create an Attribute Map</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1639,19 +1639,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>h_01KSNE06X1CQDVNKFBAGKV24AH</t>
+          <t>h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KSNE06X1CQDVNKFBAGKV24AH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JX9YC5EJAWTHGPS4C3B6KHCR</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Attribute Map Analysis - End User Behaviour</t>
+          <t>Script or JSON Mapping on Refresh</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1661,63 +1661,63 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
+          <t>h_01KSNE06X1CQDVNKFBAGKV24AH</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KSNE06X1CQDVNKFBAGKV24AH</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Attribute Map Analysis - End User Behaviour</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KKBTZ2RJG0X1T8DXXRK88MZJ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Event Trigger</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J7XABC17J1MPY99NBH1B6V1C</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Schedule Trigger</t>
+          <t>Event Trigger</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1727,85 +1727,85 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01G21ZWC4JR2TC6N2EAV6H545J</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Disable or Enable Scheduled Runs</t>
+          <t>Schedule Trigger</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01KN3VJYX1RST87W49YTJNXT7Q</t>
+          <t>h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KN3VJYX1RST87W49YTJNXT7Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01GS7T9N5V7CARZ8VTRXKZKC86</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Disable or Enable Scheduled Runs</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>h_01KN3VJYX1RST87W49YTJNXT7Q</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KN3VJYX1RST87W49YTJNXT7Q</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Add Tables in Integration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01J8HSS9ZD81S2E7A7AZJSFJH1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hide Tables for Customers</t>
+          <t>Add Tables in Integration</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1815,19 +1815,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01EKHB2K4NA8PP7JZC3JJ2PBER</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Setting Table Accessibility for End Users</t>
+          <t>Hide Tables for Customers</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1837,41 +1837,41 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KHN4H4E8FYR33A2KRHV7QDRN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Integration Details</t>
+          <t>Setting Table Accessibility for End Users</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KA0DAFRQ7A8EMM60136NCH8D</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Navigating to the Sections on the Configuration Panel</t>
+          <t>Integration Details</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JEZDYYNXX2A0YYVAK37RDQYK</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Target Attributes</t>
+          <t>Navigating to the Sections on the Configuration Panel</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1903,19 +1903,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2XTBEW99BQNSJEDWNBD3DHR</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Source Attributes</t>
+          <t>Target Attributes</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1925,19 +1925,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGS46S4K2JB3JMH5Z0PPK</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mapping Options</t>
+          <t>Source Attributes</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1947,19 +1947,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRGWFGM5A5N1M6AG42HDHG</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Search by Attribute Names</t>
+          <t>Mapping Options</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1969,19 +1969,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCRHRB2HNPRRNCYR2DYV3RX</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Modify Attribute Mapping via JSON</t>
+          <t>Search by Attribute Names</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1991,19 +1991,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCT39VAPP66ZWWBVKH7N2BT</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Refresh Attribute Mapping</t>
+          <t>Modify Attribute Mapping via JSON</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2013,19 +2013,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCTEBJ4DN8DP7A1PKGV5E1G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Using Tables in Attribute Map</t>
+          <t>Refresh Attribute Mapping</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2035,19 +2035,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JXCX80722QW7Y7SR52H74DM6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Using Parameters in Attribute Map</t>
+          <t>Using Tables in Attribute Map</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K2KN1DVGC99A3PBJEAGC3VCN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Preview in Attribute Map</t>
+          <t>Using Parameters in Attribute Map</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2079,85 +2079,85 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#01K2M0XNT5CGY37GNED9ASKV1W</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Script Editor Panel</t>
+          <t>Data Preview in Attribute Map</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KEVS6K8Q24F4ZTEZFNK5AKV8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Code Suggestions</t>
+          <t>Script Editor Panel</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
+          <t>h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FM5NQ5WZAX8S1N2PEWPZ8Q</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Using AI Assistant for a Piece of Code</t>
+          <t>Code Suggestions</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KPD1YBG1NXNVPSESQ0VM4NQJ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Show Difference in Script</t>
+          <t>Using AI Assistant for a Piece of Code</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2167,41 +2167,41 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K712PVED9B22EYKPMGV09QDG</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Flow Chart Panel</t>
+          <t>Show Difference in Script</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01K6WG00GNJQRHHHE6JJ4DXB8V</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Documentation Panel</t>
+          <t>Flow Chart Panel</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8FMWC4KWTTQP2NNBPBD7M8A</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Assistant Panel</t>
+          <t>Documentation Panel</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2233,41 +2233,41 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JA4W7EYR5VF1P072440S3KJF</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Chat History</t>
+          <t>Assistant Panel</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HGKEJGC5GPX83T0KS6DH16</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Use Generated Code in Script</t>
+          <t>Chat History</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2277,19 +2277,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA05ES3PEZVA40554H5NQW</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Use Parameters as Input</t>
+          <t>Use Generated Code in Script</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA0ZDS5GZSY566N2XV0XNY</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Use Event Types as Input</t>
+          <t>Use Parameters as Input</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2321,19 +2321,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQA2V58G13GEWAE5MF3D2A2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Use Tables as Input</t>
+          <t>Use Event Types as Input</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2343,19 +2343,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS00KZ7ES68P8J3F9XG</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Upload File as Input</t>
+          <t>Use Tables as Input</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2365,19 +2365,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JQR0ZG2E17W3QMXQVHP0EZW5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Feedback to the Assistant Response</t>
+          <t>Upload File as Input</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2387,41 +2387,41 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JKD0MYS0JXRJW0HJ031PRA3Y</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Summary Panel</t>
+          <t>Feedback to the Assistant Response</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01JHQQ26T5KKYN0M3VP45MDNNZ</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>User Actions on Integrations</t>
+          <t>Summary Panel</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2431,32 +2431,54 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
+          <t>h_01J8HD1Y85STDE8E29GCVMXS8M</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01J8HD1Y85STDE8E29GCVMXS8M</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>User Actions on Integrations</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01HTM4C4A8P6EJHBQ5Y1PHPWZS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>Import Integration Access Control</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>h_01KT3D64S2S4H1K0SDRJMM5EQ6</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Integration-Studio-Guide/#h_01KT3D64S2S4H1K0SDRJMM5EQ6</t>
         </is>
